--- a/results-excel/backtest_results.xlsx
+++ b/results-excel/backtest_results.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Annual Performance" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Missing Tickers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,28 +496,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B2" t="n">
-        <v>-4.896405866476624</v>
+        <v>-10.52549099620005</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.462059856301217</v>
+        <v>-13.50619148981854</v>
       </c>
       <c r="D2" t="n">
-        <v>3.56565398982459</v>
+        <v>2.979541516837573</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.763063806380638</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-9.797854785478547</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.03479097909791</v>
-      </c>
+        <v>-9.1</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3.866657939904013</v>
+        <v>-1.425490996200052</v>
       </c>
       <c r="I2" t="n">
         <v>35.88174522990984</v>
@@ -536,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>77.44077925419879</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
         <v>60</v>
@@ -544,28 +539,24 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.379921327251707</v>
+        <v>-11.8536199604649</v>
       </c>
       <c r="C3" t="n">
-        <v>-9.268555788706244</v>
+        <v>-13.58271174917598</v>
       </c>
       <c r="D3" t="n">
-        <v>1.888634461454539</v>
+        <v>1.726922249882319</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.15914913438398</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-11.26465336542194</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.105504231037963</v>
-      </c>
+        <v>-11.89</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2.779227807132274</v>
+        <v>0.03638003953510172</v>
       </c>
       <c r="I3" t="n">
         <v>38.75841929218824</v>
@@ -583,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>82.51906282308819</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
         <v>60</v>
@@ -591,28 +582,24 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>-23.94498441368076</v>
+        <v>-22.99911160770736</v>
       </c>
       <c r="C4" t="n">
-        <v>-26.3451117055298</v>
+        <v>-25.30241945726711</v>
       </c>
       <c r="D4" t="n">
-        <v>2.400127291849039</v>
+        <v>2.301091523696105</v>
       </c>
       <c r="E4" t="n">
-        <v>-22.33359300614559</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-23.63022591534666</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.296632909201073</v>
-      </c>
+        <v>-22.1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>-1.611391407535177</v>
+        <v>-0.8991116077073542</v>
       </c>
       <c r="I4" t="n">
         <v>40.50861655160997</v>
@@ -630,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>85.60461695248989</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
         <v>60</v>
@@ -638,28 +625,24 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>23.47242501815701</v>
+        <v>23.04444600102246</v>
       </c>
       <c r="C5" t="n">
-        <v>19.89602965587105</v>
+        <v>19.71209876326909</v>
       </c>
       <c r="D5" t="n">
-        <v>3.576395362285965</v>
+        <v>3.332511002207112</v>
       </c>
       <c r="E5" t="n">
-        <v>23.98155265180631</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22.19172065444165</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.789831997364665</v>
-      </c>
+        <v>28.68</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>-0.5091276336493031</v>
+        <v>-5.635553998977539</v>
       </c>
       <c r="I5" t="n">
         <v>41.02983047854167</v>
@@ -677,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>85.13658588451686</v>
+        <v>100</v>
       </c>
       <c r="O5" t="n">
         <v>60</v>
@@ -685,28 +668,24 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>10.04375543420985</v>
+        <v>9.977587210205572</v>
       </c>
       <c r="C6" t="n">
-        <v>6.762682628882812</v>
+        <v>6.844700039677869</v>
       </c>
       <c r="D6" t="n">
-        <v>3.281072805327039</v>
+        <v>3.130713108929453</v>
       </c>
       <c r="E6" t="n">
-        <v>10.64191315292637</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8.666726602535288</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.975186550391082</v>
-      </c>
+        <v>10.88</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>-0.5981577187165144</v>
+        <v>-0.902412789794429</v>
       </c>
       <c r="I6" t="n">
         <v>43.42485340092188</v>
@@ -724,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>91.06301493548946</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
         <v>60</v>
@@ -732,28 +711,24 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>2.122381766592819</v>
+        <v>1.933465789967272</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7627470827596737</v>
+        <v>-0.8709016808749677</v>
       </c>
       <c r="D7" t="n">
-        <v>2.885128849352493</v>
+        <v>2.803904534428515</v>
       </c>
       <c r="E7" t="n">
-        <v>5.285951787198677</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.499584372402334</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.786367414796343</v>
-      </c>
+        <v>4.91</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-3.163570020605858</v>
+        <v>-2.976534210032729</v>
       </c>
       <c r="I7" t="n">
         <v>45.53284177840612</v>
@@ -771,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>94.05697063367073</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
         <v>60</v>
@@ -779,28 +754,24 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>14.29568338944332</v>
+        <v>13.70332558080793</v>
       </c>
       <c r="C8" t="n">
-        <v>11.68477044830784</v>
+        <v>11.14622429069041</v>
       </c>
       <c r="D8" t="n">
-        <v>2.610912941135481</v>
+        <v>2.556999929197793</v>
       </c>
       <c r="E8" t="n">
-        <v>13.70639305445935</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11.77584846093133</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.930544593528019</v>
-      </c>
+        <v>15.79</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.5892903349839678</v>
+        <v>-2.086674419192072</v>
       </c>
       <c r="I8" t="n">
         <v>47.18838431687644</v>
@@ -818,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>94.69991601813588</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
         <v>60</v>
@@ -826,28 +797,24 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>11.30700215485847</v>
+        <v>9.430931663130986</v>
       </c>
       <c r="C9" t="n">
-        <v>4.875679654108497</v>
+        <v>3.219819903382591</v>
       </c>
       <c r="D9" t="n">
-        <v>6.431322500749972</v>
+        <v>6.231250619937311</v>
       </c>
       <c r="E9" t="n">
-        <v>5.334229327297166</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.423640093372005</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.910589233925161</v>
-      </c>
+        <v>5.49</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5.972772827561302</v>
+        <v>3.940931663130986</v>
       </c>
       <c r="I9" t="n">
         <v>45.99605802065285</v>
@@ -865,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>94.31499069098686</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
         <v>60</v>
@@ -873,28 +840,24 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>-28.48280575898773</v>
+        <v>-29.64754988133485</v>
       </c>
       <c r="C10" t="n">
-        <v>-33.77900691516768</v>
+        <v>-34.74418854468603</v>
       </c>
       <c r="D10" t="n">
-        <v>5.296201156179954</v>
+        <v>5.152409164630893</v>
       </c>
       <c r="E10" t="n">
-        <v>-35.85800041399297</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-37.73545849720556</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.877458083212585</v>
-      </c>
+        <v>-37</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>7.375194655005238</v>
+        <v>7.352450118665153</v>
       </c>
       <c r="I10" t="n">
         <v>46.45562053681084</v>
@@ -912,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>95.93021632183277</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
         <v>60</v>
@@ -920,28 +883,24 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>16.68349608922861</v>
+        <v>16.97700001204536</v>
       </c>
       <c r="C11" t="n">
-        <v>13.65313868648333</v>
+        <v>13.96801122425574</v>
       </c>
       <c r="D11" t="n">
-        <v>3.030357402745286</v>
+        <v>3.009162849010612</v>
       </c>
       <c r="E11" t="n">
-        <v>22.22138554216868</v>
-      </c>
-      <c r="F11" t="n">
-        <v>19.87951807228916</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.341867469879518</v>
-      </c>
+        <v>26.46</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>-5.537889452940068</v>
+        <v>-9.482999987954646</v>
       </c>
       <c r="I11" t="n">
         <v>42.48514837560866</v>
@@ -959,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>96.62141055025306</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
         <v>60</v>
@@ -967,28 +926,24 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>9.42627748509862</v>
+        <v>9.19860258597023</v>
       </c>
       <c r="C12" t="n">
-        <v>6.966778416124773</v>
+        <v>6.760062501035564</v>
       </c>
       <c r="D12" t="n">
-        <v>2.459499068973845</v>
+        <v>2.430992992332452</v>
       </c>
       <c r="E12" t="n">
-        <v>12.958616429895</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10.9591458572311</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.999470572663902</v>
-      </c>
+        <v>15.06</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>-3.532338944796379</v>
+        <v>-5.861397414029771</v>
       </c>
       <c r="I12" t="n">
         <v>45.17063017820425</v>
@@ -1006,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>98.29302526492555</v>
+        <v>100</v>
       </c>
       <c r="O12" t="n">
         <v>60</v>
@@ -1014,28 +969,24 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>2.521217025304411</v>
+        <v>2.486255929487801</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.110050431771988</v>
+        <v>-0.1341393335045956</v>
       </c>
       <c r="D13" t="n">
-        <v>2.631267457076399</v>
+        <v>2.620395262992397</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8075560802833555</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.219992129083036</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.027548209366391</v>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.713660945021056</v>
+        <v>0.3762559294878014</v>
       </c>
       <c r="I13" t="n">
         <v>46.44260294899527</v>
@@ -1053,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>99.58680771676163</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
         <v>60</v>
@@ -1061,28 +1012,24 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>16.43903652500794</v>
+        <v>16.45095793784687</v>
       </c>
       <c r="C14" t="n">
-        <v>11.05190602625681</v>
+        <v>11.12673096920813</v>
       </c>
       <c r="D14" t="n">
-        <v>5.387130498751118</v>
+        <v>5.324226968638733</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1278431372549</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11.69411764705882</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.433725490196078</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>2.311193387753036</v>
+        <v>0.4509579378468658</v>
       </c>
       <c r="I14" t="n">
         <v>46.04995550710298</v>
@@ -1100,7 +1047,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>98.83233699040764</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
         <v>60</v>
@@ -1108,28 +1055,24 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>28.81158956400206</v>
+        <v>28.79620612952294</v>
       </c>
       <c r="C15" t="n">
-        <v>22.95690474205343</v>
+        <v>23.07599060359207</v>
       </c>
       <c r="D15" t="n">
-        <v>5.854684821948629</v>
+        <v>5.720215525930871</v>
       </c>
       <c r="E15" t="n">
-        <v>28.74229768588251</v>
-      </c>
-      <c r="F15" t="n">
-        <v>26.44803505408736</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.294262631795153</v>
-      </c>
+        <v>32.39</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.06929187811954662</v>
+        <v>-3.593793870477057</v>
       </c>
       <c r="I15" t="n">
         <v>46.93431729914201</v>
@@ -1147,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>97.53157315743536</v>
+        <v>100</v>
       </c>
       <c r="O15" t="n">
         <v>60</v>
@@ -1155,28 +1098,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>15.81809779733716</v>
+        <v>15.74490342470399</v>
       </c>
       <c r="C16" t="n">
-        <v>11.64629224533519</v>
+        <v>11.62549107212051</v>
       </c>
       <c r="D16" t="n">
-        <v>4.171805552001971</v>
+        <v>4.119412352583482</v>
       </c>
       <c r="E16" t="n">
-        <v>14.4631532910562</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12.36606166630221</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.097091624753991</v>
-      </c>
+        <v>13.69</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1.354944506280955</v>
+        <v>2.054903424703992</v>
       </c>
       <c r="I16" t="n">
         <v>49.07798020703141</v>
@@ -1194,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>98.7441121412443</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
         <v>60</v>
@@ -1202,7 +1141,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B17" t="n">
         <v>5.944329654724088</v>
@@ -1214,16 +1153,12 @@
         <v>2.89200605836121</v>
       </c>
       <c r="E17" t="n">
-        <v>1.288029985883268</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-0.7593827581171213</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.04741274400039</v>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>4.65629966884082</v>
+        <v>4.564329654724088</v>
       </c>
       <c r="I17" t="n">
         <v>50.13347864718618</v>
@@ -1249,7 +1184,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B18" t="n">
         <v>12.91286635674778</v>
@@ -1261,16 +1196,12 @@
         <v>2.991308647497103</v>
       </c>
       <c r="E18" t="n">
-        <v>13.45587503730972</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11.19789075713859</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.257984280171127</v>
-      </c>
+        <v>11.96</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-0.5430086805619414</v>
+        <v>0.9528663567477746</v>
       </c>
       <c r="I18" t="n">
         <v>47.9578978407844</v>
@@ -1296,7 +1227,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B19" t="n">
         <v>22.36374349342604</v>
@@ -1308,16 +1239,12 @@
         <v>2.913581272756864</v>
       </c>
       <c r="E19" t="n">
-        <v>20.61001598295152</v>
-      </c>
-      <c r="F19" t="n">
-        <v>18.47806783874978</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.13194814420174</v>
-      </c>
+        <v>21.83</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1.753727510474519</v>
+        <v>0.5337434934260408</v>
       </c>
       <c r="I19" t="n">
         <v>48.42161818409161</v>
@@ -1343,7 +1270,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B20" t="n">
         <v>-2.53417524006105</v>
@@ -1355,16 +1282,12 @@
         <v>2.782401986504317</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.115526286415894</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-7.013431558581686</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.897905272165792</v>
-      </c>
+        <v>-4.38</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.581351046354844</v>
+        <v>1.84582475993895</v>
       </c>
       <c r="I20" t="n">
         <v>47.43684633420839</v>
@@ -1390,7 +1313,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="n">
         <v>32.74543223833429</v>
@@ -1402,16 +1325,12 @@
         <v>3.133823983727269</v>
       </c>
       <c r="E21" t="n">
-        <v>30.89735390518827</v>
-      </c>
-      <c r="F21" t="n">
-        <v>28.65137101287074</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.245982892317531</v>
-      </c>
+        <v>31.49</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.84807833314602</v>
+        <v>1.25543223833429</v>
       </c>
       <c r="I21" t="n">
         <v>45.50548630255311</v>
@@ -1437,7 +1356,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="n">
         <v>17.09049849505637</v>
@@ -1449,16 +1368,12 @@
         <v>2.535691172015732</v>
       </c>
       <c r="E22" t="n">
-        <v>16.83781204789608</v>
-      </c>
-      <c r="F22" t="n">
-        <v>15.0860344137655</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.751777634130575</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2526864471602899</v>
+        <v>-1.309501504943629</v>
       </c>
       <c r="I22" t="n">
         <v>44.83786754564369</v>
@@ -1484,7 +1399,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="n">
         <v>29.17815654196793</v>
@@ -1496,16 +1411,12 @@
         <v>2.278613775031675</v>
       </c>
       <c r="E23" t="n">
-        <v>30.33921744081997</v>
-      </c>
-      <c r="F23" t="n">
-        <v>28.78874156023752</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.550475880582445</v>
-      </c>
+        <v>28.71</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>-1.161060898852039</v>
+        <v>0.4681565419679252</v>
       </c>
       <c r="I23" t="n">
         <v>41.81514111784848</v>
@@ -1531,7 +1442,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B24" t="n">
         <v>-18.49776609950486</v>
@@ -1543,16 +1454,12 @@
         <v>1.911702283709529</v>
       </c>
       <c r="E24" t="n">
-        <v>-18.62217663435975</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-19.94515501036193</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.322978376002177</v>
-      </c>
+        <v>-18.11</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.1244105348548956</v>
+        <v>-0.3877660995048586</v>
       </c>
       <c r="I24" t="n">
         <v>41.60996806963041</v>
@@ -1578,7 +1485,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B25" t="n">
         <v>30.8031440137597</v>
@@ -1590,16 +1497,12 @@
         <v>2.456805243333683</v>
       </c>
       <c r="E25" t="n">
-        <v>26.5542277191324</v>
-      </c>
-      <c r="F25" t="n">
-        <v>24.81224725592143</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.741980463210966</v>
-      </c>
+        <v>26.29</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>4.248916294627303</v>
+        <v>4.513144013759703</v>
       </c>
       <c r="I25" t="n">
         <v>44.69222628835399</v>
@@ -1625,7 +1528,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="n">
         <v>27.67781993623965</v>
@@ -1637,16 +1540,12 @@
         <v>1.779076688872725</v>
       </c>
       <c r="E26" t="n">
-        <v>25.49350259176982</v>
-      </c>
-      <c r="F26" t="n">
-        <v>23.99873056172645</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.494772030043373</v>
-      </c>
+        <v>25.02</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2.184317344469832</v>
+        <v>2.657819936239655</v>
       </c>
       <c r="I26" t="n">
         <v>40.36115447201875</v>
@@ -1672,7 +1571,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="n">
         <v>19.6539137648381</v>
@@ -1684,16 +1583,12 @@
         <v>1.256157938486705</v>
       </c>
       <c r="E27" t="n">
-        <v>17.88470340722495</v>
-      </c>
-      <c r="F27" t="n">
-        <v>16.63929939792008</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.245404009304871</v>
-      </c>
+        <v>17.88</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.769210357613144</v>
+        <v>1.773913764838099</v>
       </c>
       <c r="I27" t="n">
         <v>36.49727522889643</v>
@@ -1785,25 +1680,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>797.2438058186283</v>
+        <v>677.4865391660518</v>
       </c>
       <c r="B2" t="n">
-        <v>8.805388165600236</v>
+        <v>8.207513726779991</v>
       </c>
       <c r="C2" t="n">
-        <v>236.8932907427337</v>
+        <v>24.64046501126234</v>
       </c>
       <c r="D2" t="n">
-        <v>560.3505150758946</v>
+        <v>652.8460741547894</v>
       </c>
       <c r="E2" t="n">
-        <v>7.530035521023004</v>
+        <v>8.073562800842504</v>
       </c>
       <c r="F2" t="n">
         <v>44.23869092896992</v>
       </c>
       <c r="G2" t="n">
-        <v>95.78366997443989</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>2.000000000000011</v>
@@ -1813,1002 +1708,6 @@
       </c>
       <c r="J2" t="n">
         <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>WCOEQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NRTLQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RDPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JAVAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LBTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>WLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S.XX1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CBS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RDPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NRTLQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JAVAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PARAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ENRNQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>RDPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>WCOEQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>JAVAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FBF</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>WAMUQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>FBF</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>BUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>LBTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>TFCFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>S.XX1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LBTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CMCSK</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>MER</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>S.XX1</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>WB.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>MON</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>WYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>MON</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>MON</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TFCFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TFCFA</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/results-excel/backtest_results.xlsx
+++ b/results-excel/backtest_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,65 +430,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>price_return</t>
+          <t>benchmark_return</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>dividend_return</t>
+          <t>active_return</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>benchmark_return</t>
+          <t>active_share</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>benchmark_price_return</t>
+          <t>max_sector_deviation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>benchmark_dividend_return</t>
+          <t>max_ig_deviation</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>active_return</t>
+          <t>passed_sector_constraint</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>active_share</t>
+          <t>passed_ig_constraint</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>max_sector_deviation</t>
+          <t>coverage_pct</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>max_ig_deviation</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>passed_sector_constraint</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>passed_ig_constraint</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>coverage_pct</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>n_stocks</t>
         </is>
@@ -499,41 +479,33 @@
         <v>2000</v>
       </c>
       <c r="B2" t="n">
-        <v>-10.52549099620005</v>
+        <v>-12.68959958663498</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.50619148981854</v>
+        <v>-9.1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.979541516837573</v>
+        <v>-3.589599586634984</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>-1.425490996200052</v>
-      </c>
-      <c r="I2" t="n">
         <v>35.88174522990984</v>
       </c>
+      <c r="F2" t="n">
+        <v>2.000000000000011</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
       <c r="J2" t="n">
-        <v>2.000000000000011</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>100</v>
-      </c>
-      <c r="O2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -542,41 +514,33 @@
         <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>-11.8536199604649</v>
+        <v>-13.78670946962385</v>
       </c>
       <c r="C3" t="n">
-        <v>-13.58271174917598</v>
+        <v>-11.89</v>
       </c>
       <c r="D3" t="n">
-        <v>1.726922249882319</v>
+        <v>-1.896709469623854</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.89</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>0.03638003953510172</v>
-      </c>
-      <c r="I3" t="n">
         <v>38.75841929218824</v>
       </c>
+      <c r="F3" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
       <c r="J3" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
         <v>60</v>
       </c>
     </row>
@@ -585,41 +549,33 @@
         <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>-22.99911160770736</v>
+        <v>-22.8047545975154</v>
       </c>
       <c r="C4" t="n">
-        <v>-25.30241945726711</v>
+        <v>-22.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.301091523696105</v>
+        <v>-0.7047545975154001</v>
       </c>
       <c r="E4" t="n">
-        <v>-22.1</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>-0.8991116077073542</v>
-      </c>
-      <c r="I4" t="n">
         <v>40.50861655160997</v>
       </c>
+      <c r="F4" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.000000000000007</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
-        <v>2.000000000000005</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>2.000000000000007</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>100</v>
-      </c>
-      <c r="O4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -628,41 +584,33 @@
         <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>23.04444600102246</v>
+        <v>25.97420939705834</v>
       </c>
       <c r="C5" t="n">
-        <v>19.71209876326909</v>
+        <v>28.68</v>
       </c>
       <c r="D5" t="n">
-        <v>3.332511002207112</v>
+        <v>-2.705790602941658</v>
       </c>
       <c r="E5" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>-5.635553998977539</v>
-      </c>
-      <c r="I5" t="n">
         <v>41.02983047854167</v>
       </c>
+      <c r="F5" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" t="n">
-        <v>2.000000000000001</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>100</v>
-      </c>
-      <c r="O5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -671,41 +619,33 @@
         <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>9.977587210205572</v>
+        <v>9.388976511728519</v>
       </c>
       <c r="C6" t="n">
-        <v>6.844700039677869</v>
+        <v>10.88</v>
       </c>
       <c r="D6" t="n">
-        <v>3.130713108929453</v>
+        <v>-1.491023488271482</v>
       </c>
       <c r="E6" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>-0.902412789794429</v>
-      </c>
-      <c r="I6" t="n">
         <v>43.42485340092188</v>
       </c>
+      <c r="F6" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
       <c r="J6" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>2.000000000000002</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>100</v>
-      </c>
-      <c r="O6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -714,41 +654,33 @@
         <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>1.933465789967272</v>
+        <v>1.382717571470944</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8709016808749677</v>
+        <v>4.91</v>
       </c>
       <c r="D7" t="n">
-        <v>2.803904534428515</v>
+        <v>-3.527282428529056</v>
       </c>
       <c r="E7" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>-2.976534210032729</v>
-      </c>
-      <c r="I7" t="n">
         <v>45.53284177840612</v>
       </c>
+      <c r="F7" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
       <c r="J7" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>100</v>
-      </c>
-      <c r="O7" t="n">
         <v>60</v>
       </c>
     </row>
@@ -757,41 +689,33 @@
         <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>13.70332558080793</v>
+        <v>16.09894671626479</v>
       </c>
       <c r="C8" t="n">
-        <v>11.14622429069041</v>
+        <v>15.79</v>
       </c>
       <c r="D8" t="n">
-        <v>2.556999929197793</v>
+        <v>0.3089467162647885</v>
       </c>
       <c r="E8" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>-2.086674419192072</v>
-      </c>
-      <c r="I8" t="n">
         <v>47.18838431687644</v>
       </c>
+      <c r="F8" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" t="n">
-        <v>2.000000000000005</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>100</v>
-      </c>
-      <c r="O8" t="n">
         <v>60</v>
       </c>
     </row>
@@ -800,41 +724,33 @@
         <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>9.430931663130986</v>
+        <v>6.005867904111259</v>
       </c>
       <c r="C9" t="n">
-        <v>3.219819903382591</v>
+        <v>5.49</v>
       </c>
       <c r="D9" t="n">
-        <v>6.231250619937311</v>
+        <v>0.5158679041112588</v>
       </c>
       <c r="E9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>3.940931663130986</v>
-      </c>
-      <c r="I9" t="n">
         <v>45.99605802065285</v>
       </c>
+      <c r="F9" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
       <c r="J9" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>2.000000000000001</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>100</v>
-      </c>
-      <c r="O9" t="n">
         <v>60</v>
       </c>
     </row>
@@ -843,41 +759,33 @@
         <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>-29.64754988133485</v>
+        <v>-33.7345293201338</v>
       </c>
       <c r="C10" t="n">
-        <v>-34.74418854468603</v>
+        <v>-37</v>
       </c>
       <c r="D10" t="n">
-        <v>5.152409164630893</v>
+        <v>3.265470679866205</v>
       </c>
       <c r="E10" t="n">
-        <v>-37</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>7.352450118665153</v>
-      </c>
-      <c r="I10" t="n">
         <v>46.45562053681084</v>
       </c>
+      <c r="F10" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" t="n">
-        <v>2.000000000000001</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>2.000000000000001</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>100</v>
-      </c>
-      <c r="O10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -886,41 +794,33 @@
         <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>16.97700001204536</v>
+        <v>20.72737264474318</v>
       </c>
       <c r="C11" t="n">
-        <v>13.96801122425574</v>
+        <v>26.46</v>
       </c>
       <c r="D11" t="n">
-        <v>3.009162849010612</v>
+        <v>-5.732627355256817</v>
       </c>
       <c r="E11" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>-9.482999987954646</v>
-      </c>
-      <c r="I11" t="n">
         <v>42.48514837560866</v>
       </c>
+      <c r="F11" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.000000000000001</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
       <c r="J11" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>2.000000000000001</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>100</v>
-      </c>
-      <c r="O11" t="n">
         <v>60</v>
       </c>
     </row>
@@ -929,41 +829,33 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>9.19860258597023</v>
+        <v>10.858190355809</v>
       </c>
       <c r="C12" t="n">
-        <v>6.760062501035564</v>
+        <v>15.06</v>
       </c>
       <c r="D12" t="n">
-        <v>2.430992992332452</v>
+        <v>-4.201809644191004</v>
       </c>
       <c r="E12" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>-5.861397414029771</v>
-      </c>
-      <c r="I12" t="n">
         <v>45.17063017820425</v>
       </c>
+      <c r="F12" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
       <c r="J12" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>100</v>
-      </c>
-      <c r="O12" t="n">
         <v>60</v>
       </c>
     </row>
@@ -972,41 +864,33 @@
         <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>2.486255929487801</v>
+        <v>3.467109693648268</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1341393335045956</v>
+        <v>2.11</v>
       </c>
       <c r="D13" t="n">
-        <v>2.620395262992397</v>
+        <v>1.357109693648268</v>
       </c>
       <c r="E13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0.3762559294878014</v>
-      </c>
-      <c r="I13" t="n">
         <v>46.44260294899527</v>
       </c>
+      <c r="F13" t="n">
+        <v>2.000000000000007</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
       <c r="J13" t="n">
-        <v>2.000000000000007</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>100</v>
-      </c>
-      <c r="O13" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1015,41 +899,33 @@
         <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>16.45095793784687</v>
+        <v>17.91262893932726</v>
       </c>
       <c r="C14" t="n">
-        <v>11.12673096920813</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>5.324226968638733</v>
+        <v>1.912628939327263</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>0.4509579378468658</v>
-      </c>
-      <c r="I14" t="n">
         <v>46.04995550710298</v>
       </c>
+      <c r="F14" t="n">
+        <v>1.95784686755224</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
       <c r="J14" t="n">
-        <v>1.95784686755224</v>
+        <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>100</v>
-      </c>
-      <c r="O14" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1058,41 +934,33 @@
         <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>28.79620612952294</v>
+        <v>29.1275238721401</v>
       </c>
       <c r="C15" t="n">
-        <v>23.07599060359207</v>
+        <v>32.39</v>
       </c>
       <c r="D15" t="n">
-        <v>5.720215525930871</v>
+        <v>-3.262476127859905</v>
       </c>
       <c r="E15" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>-3.593793870477057</v>
-      </c>
-      <c r="I15" t="n">
         <v>46.93431729914201</v>
       </c>
+      <c r="F15" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
       <c r="J15" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>2.000000000000002</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>100</v>
-      </c>
-      <c r="O15" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1101,41 +969,33 @@
         <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>15.74490342470399</v>
+        <v>13.1228958335425</v>
       </c>
       <c r="C16" t="n">
-        <v>11.62549107212051</v>
+        <v>13.69</v>
       </c>
       <c r="D16" t="n">
-        <v>4.119412352583482</v>
+        <v>-0.5671041664575025</v>
       </c>
       <c r="E16" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>2.054903424703992</v>
-      </c>
-      <c r="I16" t="n">
         <v>49.07798020703141</v>
       </c>
+      <c r="F16" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
       <c r="J16" t="n">
-        <v>2.000000000000005</v>
+        <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>2.000000000000005</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>100</v>
-      </c>
-      <c r="O16" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1144,41 +1004,33 @@
         <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>5.944329654724088</v>
+        <v>5.434349704276213</v>
       </c>
       <c r="C17" t="n">
-        <v>3.052323596362877</v>
+        <v>1.38</v>
       </c>
       <c r="D17" t="n">
-        <v>2.89200605836121</v>
+        <v>4.054349704276213</v>
       </c>
       <c r="E17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>4.564329654724088</v>
-      </c>
-      <c r="I17" t="n">
         <v>50.13347864718618</v>
       </c>
+      <c r="F17" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
       <c r="J17" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>2.000000000000002</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>100</v>
-      </c>
-      <c r="O17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1187,41 +1039,33 @@
         <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>12.91286635674778</v>
+        <v>10.82735287027742</v>
       </c>
       <c r="C18" t="n">
-        <v>9.921557709250674</v>
+        <v>11.96</v>
       </c>
       <c r="D18" t="n">
-        <v>2.991308647497103</v>
+        <v>-1.132647129722582</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0.9528663567477746</v>
-      </c>
-      <c r="I18" t="n">
         <v>47.9578978407844</v>
       </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>2.000000000000002</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>100</v>
-      </c>
-      <c r="O18" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1230,41 +1074,33 @@
         <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>22.36374349342604</v>
+        <v>23.04668523976071</v>
       </c>
       <c r="C19" t="n">
-        <v>19.45016222066917</v>
+        <v>21.83</v>
       </c>
       <c r="D19" t="n">
-        <v>2.913581272756864</v>
+        <v>1.216685239760714</v>
       </c>
       <c r="E19" t="n">
-        <v>21.83</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0.5337434934260408</v>
-      </c>
-      <c r="I19" t="n">
         <v>48.42161818409161</v>
       </c>
+      <c r="F19" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
       <c r="J19" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>2.000000000000002</v>
-      </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>100</v>
-      </c>
-      <c r="O19" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1273,41 +1109,33 @@
         <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.53417524006105</v>
+        <v>-2.53223033731219</v>
       </c>
       <c r="C20" t="n">
-        <v>-5.316577226565367</v>
+        <v>-4.38</v>
       </c>
       <c r="D20" t="n">
-        <v>2.782401986504317</v>
+        <v>1.84776966268781</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.38</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
-        <v>1.84582475993895</v>
-      </c>
-      <c r="I20" t="n">
         <v>47.43684633420839</v>
       </c>
+      <c r="F20" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.999999999999998</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
       <c r="J20" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>1.999999999999998</v>
-      </c>
-      <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>100</v>
-      </c>
-      <c r="O20" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1316,41 +1144,33 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>32.74543223833429</v>
+        <v>32.55406884618817</v>
       </c>
       <c r="C21" t="n">
-        <v>29.61160825460702</v>
+        <v>31.49</v>
       </c>
       <c r="D21" t="n">
-        <v>3.133823983727269</v>
+        <v>1.064068846188167</v>
       </c>
       <c r="E21" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>1.25543223833429</v>
-      </c>
-      <c r="I21" t="n">
         <v>45.50548630255311</v>
       </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>100</v>
-      </c>
-      <c r="O21" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1359,41 +1179,33 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>17.09049849505637</v>
+        <v>18.12353493137107</v>
       </c>
       <c r="C22" t="n">
-        <v>14.55480732304064</v>
+        <v>18.4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.535691172015732</v>
+        <v>-0.2764650686289301</v>
       </c>
       <c r="E22" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
-        <v>-1.309501504943629</v>
-      </c>
-      <c r="I22" t="n">
         <v>44.83786754564369</v>
       </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>2.000000000000005</v>
-      </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>100</v>
-      </c>
-      <c r="O22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1402,41 +1214,33 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>29.17815654196793</v>
+        <v>27.09772981691429</v>
       </c>
       <c r="C23" t="n">
-        <v>26.89954276693625</v>
+        <v>28.71</v>
       </c>
       <c r="D23" t="n">
-        <v>2.278613775031675</v>
+        <v>-1.612270183085712</v>
       </c>
       <c r="E23" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
-        <v>0.4681565419679252</v>
-      </c>
-      <c r="I23" t="n">
         <v>41.81514111784848</v>
       </c>
+      <c r="F23" t="n">
+        <v>2.000000000000005</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
       <c r="J23" t="n">
-        <v>2.000000000000005</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L23" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>100</v>
-      </c>
-      <c r="O23" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1445,41 +1249,33 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>-18.49776609950486</v>
+        <v>-18.38257793669661</v>
       </c>
       <c r="C24" t="n">
-        <v>-20.40946838321439</v>
+        <v>-18.11</v>
       </c>
       <c r="D24" t="n">
-        <v>1.911702283709529</v>
+        <v>-0.2725779366966066</v>
       </c>
       <c r="E24" t="n">
-        <v>-18.11</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
-        <v>-0.3877660995048586</v>
-      </c>
-      <c r="I24" t="n">
         <v>41.60996806963041</v>
       </c>
+      <c r="F24" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
       <c r="J24" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>100</v>
-      </c>
-      <c r="O24" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1488,41 +1284,33 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>30.8031440137597</v>
+        <v>28.99656497720724</v>
       </c>
       <c r="C25" t="n">
-        <v>28.34633877042602</v>
+        <v>26.29</v>
       </c>
       <c r="D25" t="n">
-        <v>2.456805243333683</v>
+        <v>2.70656497720724</v>
       </c>
       <c r="E25" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>4.513144013759703</v>
-      </c>
-      <c r="I25" t="n">
         <v>44.69222628835399</v>
       </c>
+      <c r="F25" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
       <c r="J25" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="b">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>100</v>
-      </c>
-      <c r="O25" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1531,41 +1319,33 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>27.67781993623965</v>
+        <v>26.72484234836757</v>
       </c>
       <c r="C26" t="n">
-        <v>25.89874324736693</v>
+        <v>25.02</v>
       </c>
       <c r="D26" t="n">
-        <v>1.779076688872725</v>
+        <v>1.704842348367571</v>
       </c>
       <c r="E26" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>2.657819936239655</v>
-      </c>
-      <c r="I26" t="n">
         <v>40.36115447201875</v>
       </c>
+      <c r="F26" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.000000000000007</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
       <c r="J26" t="n">
-        <v>2.000000000000004</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>2.000000000000007</v>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" t="b">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>100</v>
-      </c>
-      <c r="O26" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1574,41 +1354,33 @@
         <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>19.6539137648381</v>
+        <v>19.50285254213123</v>
       </c>
       <c r="C27" t="n">
-        <v>18.3977558263514</v>
+        <v>17.88</v>
       </c>
       <c r="D27" t="n">
-        <v>1.256157938486705</v>
+        <v>1.622852542131231</v>
       </c>
       <c r="E27" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>1.773913764838099</v>
-      </c>
-      <c r="I27" t="n">
         <v>36.49727522889643</v>
       </c>
+      <c r="F27" t="n">
+        <v>2.000000000000002</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.000000000000004</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
       <c r="J27" t="n">
-        <v>2.000000000000002</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>2.000000000000004</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="b">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>100</v>
-      </c>
-      <c r="O27" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1680,13 +1452,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>677.4865391660518</v>
+        <v>602.1489317039319</v>
       </c>
       <c r="B2" t="n">
-        <v>8.207513726779991</v>
+        <v>7.784167267876363</v>
       </c>
       <c r="C2" t="n">
-        <v>24.64046501126234</v>
+        <v>-50.69714245085759</v>
       </c>
       <c r="D2" t="n">
         <v>652.8460741547894</v>
